--- a/database/event/3530/event_3530_evp_summary.xlsx
+++ b/database/event/3530/event_3530_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.119899999999999</v>
+        <v>9.191000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>4.0714</v>
+        <v>4.1031</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2629</v>
+        <v>3.2178</v>
       </c>
       <c r="E2" t="n">
-        <v>9.119899999999999</v>
+        <v>9.191000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>4.5552</v>
+        <v>4.6263</v>
       </c>
       <c r="G2" t="n">
         <v>4.5647</v>
       </c>
       <c r="H2" t="n">
-        <v>4.8395</v>
+        <v>4.951</v>
       </c>
       <c r="I2" t="n">
-        <v>4.9074</v>
+        <v>5.077</v>
       </c>
       <c r="J2" t="n">
         <v>4.5647</v>
@@ -529,7 +529,7 @@
         <v>237</v>
       </c>
       <c r="M2" t="n">
-        <v>9.472100000000001</v>
+        <v>9.6417</v>
       </c>
       <c r="N2" t="n">
         <v>490</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.2417</v>
+        <v>8.8392</v>
       </c>
       <c r="C3" t="n">
-        <v>3.6793</v>
+        <v>3.9461</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9081</v>
+        <v>3.0776</v>
       </c>
       <c r="E3" t="n">
-        <v>8.2417</v>
+        <v>8.8392</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1439</v>
+        <v>3.7414</v>
       </c>
       <c r="G3" t="n">
         <v>5.0978</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1439</v>
+        <v>3.7414</v>
       </c>
       <c r="I3" t="n">
-        <v>3.188</v>
+        <v>3.8367</v>
       </c>
       <c r="J3" t="n">
         <v>5.0978</v>
@@ -575,7 +575,7 @@
         <v>237</v>
       </c>
       <c r="M3" t="n">
-        <v>8.2858</v>
+        <v>8.9345</v>
       </c>
       <c r="N3" t="n">
         <v>490</v>
@@ -594,7 +594,7 @@
         <v>3.1567</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4352</v>
+        <v>2.3732</v>
       </c>
       <c r="E4" t="n">
         <v>7.071</v>
@@ -630,93 +630,93 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.3868</v>
+        <v>6.4653</v>
       </c>
       <c r="C5" t="n">
-        <v>2.8513</v>
+        <v>2.8863</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1588</v>
+        <v>2.1319</v>
       </c>
       <c r="E5" t="n">
-        <v>6.3868</v>
+        <v>6.4653</v>
       </c>
       <c r="F5" t="n">
-        <v>4.1657</v>
+        <v>4.1393</v>
       </c>
       <c r="G5" t="n">
-        <v>2.221</v>
+        <v>2.326</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1991</v>
+        <v>4.1874</v>
       </c>
       <c r="I5" t="n">
-        <v>3.4035</v>
+        <v>4.294</v>
       </c>
       <c r="J5" t="n">
-        <v>2.221</v>
+        <v>2.326</v>
       </c>
       <c r="K5" t="n">
-        <v>130</v>
+        <v>253</v>
       </c>
       <c r="L5" t="n">
-        <v>184</v>
+        <v>237</v>
       </c>
       <c r="M5" t="n">
-        <v>5.6245</v>
+        <v>6.619999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>314</v>
+        <v>490</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.9898</v>
+        <v>6.3868</v>
       </c>
       <c r="C6" t="n">
-        <v>2.674</v>
+        <v>2.8513</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9984</v>
+        <v>2.1006</v>
       </c>
       <c r="E6" t="n">
-        <v>5.9898</v>
+        <v>6.3868</v>
       </c>
       <c r="F6" t="n">
-        <v>3.6638</v>
+        <v>4.1657</v>
       </c>
       <c r="G6" t="n">
-        <v>2.326</v>
+        <v>2.221</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6638</v>
+        <v>4.1991</v>
       </c>
       <c r="I6" t="n">
-        <v>3.7152</v>
+        <v>3.4035</v>
       </c>
       <c r="J6" t="n">
-        <v>2.326</v>
+        <v>2.221</v>
       </c>
       <c r="K6" t="n">
-        <v>253</v>
+        <v>130</v>
       </c>
       <c r="L6" t="n">
-        <v>237</v>
+        <v>184</v>
       </c>
       <c r="M6" t="n">
-        <v>6.0412</v>
+        <v>5.6245</v>
       </c>
       <c r="N6" t="n">
-        <v>490</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7">
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.6085</v>
+        <v>5.847</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5038</v>
+        <v>2.6103</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8443</v>
+        <v>1.8855</v>
       </c>
       <c r="E7" t="n">
-        <v>5.6085</v>
+        <v>5.847</v>
       </c>
       <c r="F7" t="n">
-        <v>3.5645</v>
+        <v>3.8029</v>
       </c>
       <c r="G7" t="n">
         <v>2.0441</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5645</v>
+        <v>3.8029</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8891</v>
+        <v>3.0824</v>
       </c>
       <c r="J7" t="n">
         <v>2.0441</v>
@@ -759,7 +759,7 @@
         <v>184</v>
       </c>
       <c r="M7" t="n">
-        <v>4.933199999999999</v>
+        <v>5.1265</v>
       </c>
       <c r="N7" t="n">
         <v>314</v>
@@ -778,7 +778,7 @@
         <v>2.278</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6401</v>
+        <v>1.589</v>
       </c>
       <c r="E8" t="n">
         <v>5.1028</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.6814</v>
+        <v>4.7366</v>
       </c>
       <c r="C9" t="n">
-        <v>2.0899</v>
+        <v>2.1146</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4698</v>
+        <v>1.4432</v>
       </c>
       <c r="E9" t="n">
-        <v>4.6814</v>
+        <v>4.7366</v>
       </c>
       <c r="F9" t="n">
-        <v>4.5863</v>
+        <v>4.6415</v>
       </c>
       <c r="G9" t="n">
         <v>0.0951</v>
       </c>
       <c r="H9" t="n">
-        <v>5.8911</v>
+        <v>6.1133</v>
       </c>
       <c r="I9" t="n">
-        <v>4.7749</v>
+        <v>4.955</v>
       </c>
       <c r="J9" t="n">
         <v>0.0951</v>
@@ -851,7 +851,7 @@
         <v>75</v>
       </c>
       <c r="M9" t="n">
-        <v>4.87</v>
+        <v>5.0501</v>
       </c>
       <c r="N9" t="n">
         <v>218</v>
@@ -870,7 +870,7 @@
         <v>1.9049</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3024</v>
+        <v>1.2561</v>
       </c>
       <c r="E10" t="n">
         <v>4.267</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.1295</v>
+        <v>4.1032</v>
       </c>
       <c r="C11" t="n">
-        <v>1.8435</v>
+        <v>1.8318</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2469</v>
+        <v>1.1908</v>
       </c>
       <c r="E11" t="n">
-        <v>4.1295</v>
+        <v>4.1032</v>
       </c>
       <c r="F11" t="n">
-        <v>3.5901</v>
+        <v>3.5638</v>
       </c>
       <c r="G11" t="n">
         <v>0.5394</v>
       </c>
       <c r="H11" t="n">
-        <v>3.5901</v>
+        <v>3.5638</v>
       </c>
       <c r="I11" t="n">
-        <v>3.6236</v>
+        <v>3.6241</v>
       </c>
       <c r="J11" t="n">
         <v>0.5394</v>
@@ -943,7 +943,7 @@
         <v>181</v>
       </c>
       <c r="M11" t="n">
-        <v>4.163</v>
+        <v>4.1635</v>
       </c>
       <c r="N11" t="n">
         <v>347</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.4843</v>
+        <v>3.6899</v>
       </c>
       <c r="C12" t="n">
-        <v>1.5555</v>
+        <v>1.6473</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9862</v>
+        <v>1.0261</v>
       </c>
       <c r="E12" t="n">
-        <v>3.4843</v>
+        <v>3.6899</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9201</v>
+        <v>3.1257</v>
       </c>
       <c r="G12" t="n">
         <v>0.5642</v>
       </c>
       <c r="H12" t="n">
-        <v>2.9201</v>
+        <v>3.1257</v>
       </c>
       <c r="I12" t="n">
-        <v>2.9473</v>
+        <v>3.1786</v>
       </c>
       <c r="J12" t="n">
         <v>0.5642</v>
@@ -989,7 +989,7 @@
         <v>181</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5115</v>
+        <v>3.7428</v>
       </c>
       <c r="N12" t="n">
         <v>347</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.2957</v>
+        <v>3.5655</v>
       </c>
       <c r="C13" t="n">
-        <v>1.4713</v>
+        <v>1.5917</v>
       </c>
       <c r="D13" t="n">
-        <v>0.91</v>
+        <v>0.9766</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2957</v>
+        <v>3.5655</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5802</v>
+        <v>2.85</v>
       </c>
       <c r="G13" t="n">
         <v>0.7155</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5802</v>
+        <v>2.85</v>
       </c>
       <c r="I13" t="n">
-        <v>2.0913</v>
+        <v>2.31</v>
       </c>
       <c r="J13" t="n">
         <v>0.7155</v>
@@ -1035,7 +1035,7 @@
         <v>75</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8068</v>
+        <v>3.0255</v>
       </c>
       <c r="N13" t="n">
         <v>218</v>
@@ -1044,262 +1044,262 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4395</v>
+        <v>3.2804</v>
       </c>
       <c r="C14" t="n">
-        <v>1.0891</v>
+        <v>1.4645</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5641</v>
+        <v>0.863</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4395</v>
+        <v>3.2804</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4395</v>
+        <v>3.2804</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.4395</v>
+        <v>3.2804</v>
       </c>
       <c r="I14" t="n">
-        <v>2.4395</v>
+        <v>3.308</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.4395</v>
+        <v>3.308</v>
       </c>
       <c r="N14" t="n">
-        <v>209</v>
+        <v>234</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.4255</v>
+        <v>3.0273</v>
       </c>
       <c r="C15" t="n">
-        <v>1.0828</v>
+        <v>1.3515</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5585</v>
+        <v>0.7622</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4255</v>
+        <v>3.0273</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4255</v>
+        <v>3.0273</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4255</v>
+        <v>3.0273</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4368</v>
+        <v>3.0273</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>234</v>
+        <v>209</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.4368</v>
+        <v>3.0273</v>
       </c>
       <c r="N15" t="n">
-        <v>234</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2764</v>
+        <v>2.5321</v>
       </c>
       <c r="C16" t="n">
-        <v>1.0163</v>
+        <v>1.1304</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4983</v>
+        <v>0.5649</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2764</v>
+        <v>2.5321</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2764</v>
+        <v>2.5321</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2764</v>
+        <v>2.5321</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2764</v>
+        <v>2.5321</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>164</v>
+        <v>209</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.2764</v>
+        <v>2.5321</v>
       </c>
       <c r="N16" t="n">
-        <v>164</v>
+        <v>209</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Hatz</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1728</v>
+        <v>2.465</v>
       </c>
       <c r="C17" t="n">
-        <v>0.97</v>
+        <v>1.1005</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4564</v>
+        <v>0.5381</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1728</v>
+        <v>2.465</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1728</v>
+        <v>2.465</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1728</v>
+        <v>2.465</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1728</v>
+        <v>2.4858</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>156</v>
+        <v>234</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.1728</v>
+        <v>2.4858</v>
       </c>
       <c r="N17" t="n">
-        <v>156</v>
+        <v>234</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9897</v>
+        <v>2.3822</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8883</v>
+        <v>1.0635</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3824</v>
+        <v>0.5052</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9897</v>
+        <v>2.3822</v>
       </c>
       <c r="F18" t="n">
-        <v>1.999</v>
+        <v>2.4431</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0609</v>
       </c>
       <c r="H18" t="n">
-        <v>1.999</v>
+        <v>2.4431</v>
       </c>
       <c r="I18" t="n">
-        <v>2.027</v>
+        <v>2.4431</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0609</v>
       </c>
       <c r="K18" t="n">
-        <v>253</v>
+        <v>181</v>
       </c>
       <c r="L18" t="n">
-        <v>237</v>
+        <v>105</v>
       </c>
       <c r="M18" t="n">
-        <v>2.0177</v>
+        <v>2.3822</v>
       </c>
       <c r="N18" t="n">
-        <v>490</v>
+        <v>286</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.9622</v>
+        <v>2.2764</v>
       </c>
       <c r="C19" t="n">
-        <v>0.876</v>
+        <v>1.0163</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3713</v>
+        <v>0.463</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9622</v>
+        <v>2.2764</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9622</v>
+        <v>2.2764</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9622</v>
+        <v>2.2764</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9622</v>
+        <v>2.2764</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.9622</v>
+        <v>2.2764</v>
       </c>
       <c r="N19" t="n">
         <v>164</v>
@@ -1320,311 +1320,311 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>Hatz</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.824</v>
+        <v>2.1728</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8143</v>
+        <v>0.97</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3155</v>
+        <v>0.4217</v>
       </c>
       <c r="E20" t="n">
-        <v>1.824</v>
+        <v>2.1728</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5872</v>
+        <v>2.1728</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7632</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.5872</v>
+        <v>2.1728</v>
       </c>
       <c r="I20" t="n">
-        <v>2.5872</v>
+        <v>2.1728</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7632</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="L20" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.824</v>
+        <v>2.1728</v>
       </c>
       <c r="N20" t="n">
-        <v>202</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Liazz</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.82</v>
+        <v>2.1647</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8125</v>
+        <v>0.9664</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3139</v>
+        <v>0.4185</v>
       </c>
       <c r="E21" t="n">
-        <v>1.82</v>
+        <v>2.1647</v>
       </c>
       <c r="F21" t="n">
-        <v>1.82</v>
+        <v>2.9279</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.7632</v>
       </c>
       <c r="H21" t="n">
-        <v>1.82</v>
+        <v>2.9279</v>
       </c>
       <c r="I21" t="n">
-        <v>1.82</v>
+        <v>2.9279</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.7632</v>
       </c>
       <c r="K21" t="n">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M21" t="n">
-        <v>1.82</v>
+        <v>2.1647</v>
       </c>
       <c r="N21" t="n">
-        <v>156</v>
+        <v>202</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.7762</v>
+        <v>2.0412</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7929</v>
+        <v>0.9113</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2962</v>
+        <v>0.3693</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7762</v>
+        <v>2.0412</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4681</v>
+        <v>1.9085</v>
       </c>
       <c r="G22" t="n">
-        <v>1.3081</v>
+        <v>0.1327</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4681</v>
+        <v>1.9085</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4746</v>
+        <v>1.9085</v>
       </c>
       <c r="J22" t="n">
-        <v>1.3081</v>
+        <v>0.1327</v>
       </c>
       <c r="K22" t="n">
-        <v>253</v>
+        <v>181</v>
       </c>
       <c r="L22" t="n">
-        <v>237</v>
+        <v>105</v>
       </c>
       <c r="M22" t="n">
-        <v>1.7827</v>
+        <v>2.0412</v>
       </c>
       <c r="N22" t="n">
-        <v>490</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.7334</v>
+        <v>1.9674</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7738</v>
+        <v>0.8783</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2789</v>
+        <v>0.3399</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7334</v>
+        <v>1.9674</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6007</v>
+        <v>1.9767</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1327</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>1.6007</v>
+        <v>1.9767</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6007</v>
+        <v>2.027</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1327</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>181</v>
+        <v>253</v>
       </c>
       <c r="L23" t="n">
-        <v>105</v>
+        <v>237</v>
       </c>
       <c r="M23" t="n">
-        <v>1.7334</v>
+        <v>2.0177</v>
       </c>
       <c r="N23" t="n">
-        <v>286</v>
+        <v>490</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.69</v>
+        <v>1.9622</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.876</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2614</v>
+        <v>0.3378</v>
       </c>
       <c r="E24" t="n">
-        <v>1.69</v>
+        <v>1.9622</v>
       </c>
       <c r="F24" t="n">
-        <v>1.69</v>
+        <v>1.9622</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.69</v>
+        <v>1.9622</v>
       </c>
       <c r="I24" t="n">
-        <v>1.69</v>
+        <v>1.9622</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>209</v>
+        <v>164</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.69</v>
+        <v>1.9622</v>
       </c>
       <c r="N24" t="n">
-        <v>209</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.6559</v>
+        <v>1.8606</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7392</v>
+        <v>0.8306</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2476</v>
+        <v>0.2974</v>
       </c>
       <c r="E25" t="n">
-        <v>1.6559</v>
+        <v>1.8606</v>
       </c>
       <c r="F25" t="n">
-        <v>1.6559</v>
+        <v>0.5525</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1.3081</v>
       </c>
       <c r="H25" t="n">
-        <v>1.6559</v>
+        <v>0.5525</v>
       </c>
       <c r="I25" t="n">
-        <v>1.6636</v>
+        <v>0.5666</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1.3081</v>
       </c>
       <c r="K25" t="n">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="M25" t="n">
-        <v>1.6636</v>
+        <v>1.8747</v>
       </c>
       <c r="N25" t="n">
-        <v>234</v>
+        <v>490</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.6434</v>
+        <v>1.8373</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7337</v>
+        <v>0.8202</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2425</v>
+        <v>0.2881</v>
       </c>
       <c r="E26" t="n">
-        <v>1.6434</v>
+        <v>1.8373</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2767</v>
+        <v>2.3376</v>
       </c>
       <c r="G26" t="n">
-        <v>1.3667</v>
+        <v>-0.5003</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2767</v>
+        <v>2.3376</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2793</v>
+        <v>2.3771</v>
       </c>
       <c r="J26" t="n">
-        <v>1.3667</v>
+        <v>-0.5003</v>
       </c>
       <c r="K26" t="n">
         <v>166</v>
@@ -1633,7 +1633,7 @@
         <v>181</v>
       </c>
       <c r="M26" t="n">
-        <v>1.646</v>
+        <v>1.8768</v>
       </c>
       <c r="N26" t="n">
         <v>347</v>
@@ -1642,81 +1642,81 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Gratisfaction</t>
+          <t>Liazz</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.6002</v>
+        <v>1.82</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7144</v>
+        <v>0.8125</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2251</v>
+        <v>0.2812</v>
       </c>
       <c r="E27" t="n">
-        <v>1.6002</v>
+        <v>1.82</v>
       </c>
       <c r="F27" t="n">
-        <v>1.6002</v>
+        <v>1.82</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.6002</v>
+        <v>1.82</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6002</v>
+        <v>1.82</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.6002</v>
+        <v>1.82</v>
       </c>
       <c r="N27" t="n">
-        <v>187</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.5792</v>
+        <v>1.667</v>
       </c>
       <c r="C28" t="n">
-        <v>0.705</v>
+        <v>0.7442</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2166</v>
+        <v>0.2202</v>
       </c>
       <c r="E28" t="n">
-        <v>1.5792</v>
+        <v>1.667</v>
       </c>
       <c r="F28" t="n">
-        <v>2.329</v>
+        <v>2.1471</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.7498</v>
+        <v>-0.4801</v>
       </c>
       <c r="H28" t="n">
-        <v>2.329</v>
+        <v>2.1471</v>
       </c>
       <c r="I28" t="n">
-        <v>2.329</v>
+        <v>2.1471</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.7498</v>
+        <v>-0.4801</v>
       </c>
       <c r="K28" t="n">
         <v>148</v>
@@ -1725,7 +1725,7 @@
         <v>54</v>
       </c>
       <c r="M28" t="n">
-        <v>1.5792</v>
+        <v>1.667</v>
       </c>
       <c r="N28" t="n">
         <v>202</v>
@@ -1734,645 +1734,645 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.5484</v>
+        <v>1.6532</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6913</v>
+        <v>0.738</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2042</v>
+        <v>0.2147</v>
       </c>
       <c r="E29" t="n">
-        <v>1.5484</v>
+        <v>1.6532</v>
       </c>
       <c r="F29" t="n">
-        <v>1.6093</v>
+        <v>2.403</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0609</v>
+        <v>-0.7498</v>
       </c>
       <c r="H29" t="n">
-        <v>1.6093</v>
+        <v>2.403</v>
       </c>
       <c r="I29" t="n">
-        <v>1.6093</v>
+        <v>2.403</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.0609</v>
+        <v>-0.7498</v>
       </c>
       <c r="K29" t="n">
-        <v>181</v>
+        <v>148</v>
       </c>
       <c r="L29" t="n">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="M29" t="n">
-        <v>1.5484</v>
+        <v>1.6532</v>
       </c>
       <c r="N29" t="n">
-        <v>286</v>
+        <v>202</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.5192</v>
+        <v>1.6414</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6782</v>
+        <v>0.7328</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1924</v>
+        <v>0.21</v>
       </c>
       <c r="E30" t="n">
-        <v>1.5192</v>
+        <v>1.6414</v>
       </c>
       <c r="F30" t="n">
-        <v>1.5192</v>
+        <v>0.2747</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1.3667</v>
       </c>
       <c r="H30" t="n">
-        <v>1.5192</v>
+        <v>0.2747</v>
       </c>
       <c r="I30" t="n">
-        <v>1.5192</v>
+        <v>0.2793</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1.3667</v>
       </c>
       <c r="K30" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="M30" t="n">
-        <v>1.5192</v>
+        <v>1.646</v>
       </c>
       <c r="N30" t="n">
-        <v>164</v>
+        <v>347</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>Gratisfaction</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.473</v>
+        <v>1.6002</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6576</v>
+        <v>0.7144</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1737</v>
+        <v>0.1936</v>
       </c>
       <c r="E31" t="n">
-        <v>1.473</v>
+        <v>1.6002</v>
       </c>
       <c r="F31" t="n">
-        <v>1.473</v>
+        <v>1.6002</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.473</v>
+        <v>1.6002</v>
       </c>
       <c r="I31" t="n">
-        <v>1.4799</v>
+        <v>1.6002</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>234</v>
+        <v>187</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.4799</v>
+        <v>1.6002</v>
       </c>
       <c r="N31" t="n">
-        <v>234</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.3859</v>
+        <v>1.5192</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6187</v>
+        <v>0.6782</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1385</v>
+        <v>0.1613</v>
       </c>
       <c r="E32" t="n">
-        <v>1.3859</v>
+        <v>1.5192</v>
       </c>
       <c r="F32" t="n">
-        <v>1.3859</v>
+        <v>1.5192</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.3859</v>
+        <v>1.5192</v>
       </c>
       <c r="I32" t="n">
-        <v>1.3859</v>
+        <v>1.5192</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>209</v>
+        <v>164</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.3859</v>
+        <v>1.5192</v>
       </c>
       <c r="N32" t="n">
-        <v>209</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sico</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.3115</v>
+        <v>1.4891</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5855</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1085</v>
+        <v>0.1493</v>
       </c>
       <c r="E33" t="n">
-        <v>1.3115</v>
+        <v>1.4891</v>
       </c>
       <c r="F33" t="n">
-        <v>1.3115</v>
+        <v>1.4891</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.3115</v>
+        <v>1.4891</v>
       </c>
       <c r="I33" t="n">
-        <v>1.3115</v>
+        <v>1.5016</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>156</v>
+        <v>234</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.3115</v>
+        <v>1.5016</v>
       </c>
       <c r="N33" t="n">
-        <v>156</v>
+        <v>234</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.2025</v>
+        <v>1.3859</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.6187</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0644</v>
+        <v>0.1082</v>
       </c>
       <c r="E34" t="n">
-        <v>1.2025</v>
+        <v>1.3859</v>
       </c>
       <c r="F34" t="n">
-        <v>1.2025</v>
+        <v>1.3859</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.2025</v>
+        <v>1.3859</v>
       </c>
       <c r="I34" t="n">
-        <v>1.2025</v>
+        <v>1.3859</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>118</v>
+        <v>209</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.2025</v>
+        <v>1.3859</v>
       </c>
       <c r="N34" t="n">
-        <v>118</v>
+        <v>209</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>Sico</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.153</v>
+        <v>1.3115</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5147</v>
+        <v>0.5855</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0444</v>
+        <v>0.0786</v>
       </c>
       <c r="E35" t="n">
-        <v>1.153</v>
+        <v>1.3115</v>
       </c>
       <c r="F35" t="n">
-        <v>1.153</v>
+        <v>1.3115</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.153</v>
+        <v>1.3115</v>
       </c>
       <c r="I35" t="n">
-        <v>1.153</v>
+        <v>1.3115</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.153</v>
+        <v>1.3115</v>
       </c>
       <c r="N35" t="n">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>erkaSt</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.0466</v>
+        <v>1.2025</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4672</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0014</v>
+        <v>0.0352</v>
       </c>
       <c r="E36" t="n">
-        <v>1.0466</v>
+        <v>1.2025</v>
       </c>
       <c r="F36" t="n">
-        <v>1.0466</v>
+        <v>1.2025</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.0466</v>
+        <v>1.2025</v>
       </c>
       <c r="I36" t="n">
-        <v>1.0466</v>
+        <v>1.2025</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>187</v>
+        <v>118</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.0466</v>
+        <v>1.2025</v>
       </c>
       <c r="N36" t="n">
-        <v>187</v>
+        <v>118</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9653</v>
+        <v>1.153</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4309</v>
+        <v>0.5147</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0314</v>
+        <v>0.0154</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9653</v>
+        <v>1.153</v>
       </c>
       <c r="F37" t="n">
-        <v>1.4656</v>
+        <v>1.153</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.5003</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.4656</v>
+        <v>1.153</v>
       </c>
       <c r="I37" t="n">
-        <v>1.4793</v>
+        <v>1.153</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.5003</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="L37" t="n">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.9790000000000001</v>
+        <v>1.153</v>
       </c>
       <c r="N37" t="n">
-        <v>347</v>
+        <v>164</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>sterling</t>
+          <t>erkaSt</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.9498</v>
+        <v>1.0466</v>
       </c>
       <c r="C38" t="n">
-        <v>0.424</v>
+        <v>0.4672</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0377</v>
+        <v>-0.0269</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9498</v>
+        <v>1.0466</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9498</v>
+        <v>1.0466</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9498</v>
+        <v>1.0466</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9498</v>
+        <v>1.0466</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>73</v>
+        <v>187</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.9498</v>
+        <v>1.0466</v>
       </c>
       <c r="N38" t="n">
-        <v>73</v>
+        <v>187</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>XigN</t>
+          <t>sterling</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.9498</v>
       </c>
       <c r="C39" t="n">
-        <v>0.371</v>
+        <v>0.424</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0856</v>
+        <v>-0.0655</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.9498</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.9498</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.9498</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.9498</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>123</v>
+        <v>73</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.9498</v>
       </c>
       <c r="N39" t="n">
-        <v>123</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>XigN</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8290999999999999</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3701</v>
+        <v>0.371</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.0864</v>
+        <v>-0.1128</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8290999999999999</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8290999999999999</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.8290999999999999</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8290999999999999</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.8290999999999999</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>zeff</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8114</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3622</v>
+        <v>0.3701</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0936</v>
+        <v>-0.1136</v>
       </c>
       <c r="E41" t="n">
-        <v>0.8114</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8114</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.8114</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8114</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.8114</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>zeff</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7455000000000001</v>
+        <v>0.8114</v>
       </c>
       <c r="C42" t="n">
-        <v>0.3328</v>
+        <v>0.3622</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1202</v>
+        <v>-0.1206</v>
       </c>
       <c r="E42" t="n">
-        <v>0.7455000000000001</v>
+        <v>0.8114</v>
       </c>
       <c r="F42" t="n">
-        <v>1.2256</v>
+        <v>0.8114</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.4801</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.2256</v>
+        <v>0.8114</v>
       </c>
       <c r="I42" t="n">
-        <v>1.2256</v>
+        <v>0.8114</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.4801</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="L42" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.7455000000000001</v>
+        <v>0.8114</v>
       </c>
       <c r="N42" t="n">
-        <v>202</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43">
@@ -2388,7 +2388,7 @@
         <v>0.2445</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2001</v>
+        <v>-0.2257</v>
       </c>
       <c r="E43" t="n">
         <v>0.5476</v>
@@ -2434,7 +2434,7 @@
         <v>0.2282</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2149</v>
+        <v>-0.2403</v>
       </c>
       <c r="E44" t="n">
         <v>0.5111</v>
@@ -2480,7 +2480,7 @@
         <v>0.169</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2685</v>
+        <v>-0.2931</v>
       </c>
       <c r="E45" t="n">
         <v>0.3785</v>
@@ -2516,185 +2516,185 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.3338</v>
+        <v>0.3689</v>
       </c>
       <c r="C46" t="n">
-        <v>0.149</v>
+        <v>0.1647</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2865</v>
+        <v>-0.2969</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3338</v>
+        <v>0.3689</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0291</v>
+        <v>0.8107</v>
       </c>
       <c r="G46" t="n">
-        <v>0.3047</v>
+        <v>-0.4418</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0291</v>
+        <v>0.8107</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0291</v>
+        <v>0.8107</v>
       </c>
       <c r="J46" t="n">
-        <v>0.3047</v>
+        <v>-0.4418</v>
       </c>
       <c r="K46" t="n">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="L46" t="n">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="M46" t="n">
-        <v>0.3338</v>
+        <v>0.3689</v>
       </c>
       <c r="N46" t="n">
-        <v>202</v>
+        <v>286</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.319</v>
+        <v>0.3338</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1424</v>
+        <v>0.149</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2925</v>
+        <v>-0.3109</v>
       </c>
       <c r="E47" t="n">
-        <v>0.319</v>
+        <v>0.3338</v>
       </c>
       <c r="F47" t="n">
-        <v>0.319</v>
+        <v>0.0291</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>0.3047</v>
       </c>
       <c r="H47" t="n">
-        <v>0.319</v>
+        <v>0.0291</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3205</v>
+        <v>0.0291</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>0.3047</v>
       </c>
       <c r="K47" t="n">
-        <v>234</v>
+        <v>148</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M47" t="n">
-        <v>0.3205</v>
+        <v>0.3338</v>
       </c>
       <c r="N47" t="n">
-        <v>234</v>
+        <v>202</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.2123</v>
+        <v>0.3178</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0948</v>
+        <v>0.1419</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3356</v>
+        <v>-0.3173</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2123</v>
+        <v>0.3178</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2123</v>
+        <v>0.3178</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2123</v>
+        <v>0.3178</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2123</v>
+        <v>0.3205</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>118</v>
+        <v>234</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.2123</v>
+        <v>0.3205</v>
       </c>
       <c r="N48" t="n">
-        <v>118</v>
+        <v>234</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.0945</v>
+        <v>0.2123</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0422</v>
+        <v>0.0948</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3832</v>
+        <v>-0.3593</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0945</v>
+        <v>0.2123</v>
       </c>
       <c r="F49" t="n">
-        <v>0.5363</v>
+        <v>0.2123</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.4418</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.5363</v>
+        <v>0.2123</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5363</v>
+        <v>0.2123</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.4418</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>181</v>
+        <v>118</v>
       </c>
       <c r="L49" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.09449999999999997</v>
+        <v>0.2123</v>
       </c>
       <c r="N49" t="n">
-        <v>286</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50">
@@ -2710,7 +2710,7 @@
         <v>0.0252</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3986</v>
+        <v>-0.4214</v>
       </c>
       <c r="E50" t="n">
         <v>0.0564</v>
@@ -2756,7 +2756,7 @@
         <v>-0.0146</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4345</v>
+        <v>-0.4569</v>
       </c>
       <c r="E51" t="n">
         <v>-0.0326</v>
@@ -2796,28 +2796,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.1827</v>
+        <v>-0.1826</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.0815</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4952</v>
+        <v>-0.5167</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.1827</v>
+        <v>-0.1826</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.031</v>
+        <v>-0.0309</v>
       </c>
       <c r="G52" t="n">
         <v>-0.1517</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.031</v>
+        <v>-0.0309</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.031</v>
+        <v>-0.0309</v>
       </c>
       <c r="J52" t="n">
         <v>-0.1517</v>
@@ -2829,7 +2829,7 @@
         <v>54</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.1827</v>
+        <v>-0.1826</v>
       </c>
       <c r="N52" t="n">
         <v>202</v>
@@ -2848,7 +2848,7 @@
         <v>-0.1217</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5315</v>
+        <v>-0.5525</v>
       </c>
       <c r="E53" t="n">
         <v>-0.2726</v>
@@ -2894,7 +2894,7 @@
         <v>-0.1275</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5368000000000001</v>
+        <v>-0.5577</v>
       </c>
       <c r="E54" t="n">
         <v>-0.2857</v>
@@ -2940,7 +2940,7 @@
         <v>-0.1858</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5895</v>
+        <v>-0.6097</v>
       </c>
       <c r="E55" t="n">
         <v>-0.4161</v>
@@ -2986,7 +2986,7 @@
         <v>-0.2134</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6145</v>
+        <v>-0.6344</v>
       </c>
       <c r="E56" t="n">
         <v>-0.4781</v>
@@ -3032,7 +3032,7 @@
         <v>-0.2559</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.653</v>
+        <v>-0.6723</v>
       </c>
       <c r="E57" t="n">
         <v>-0.5733</v>
@@ -3078,7 +3078,7 @@
         <v>-0.2768</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="E58" t="n">
         <v>-0.6201</v>
@@ -3124,7 +3124,7 @@
         <v>-0.2933</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6867</v>
+        <v>-0.7056</v>
       </c>
       <c r="E59" t="n">
         <v>-0.6569</v>
@@ -3164,25 +3164,25 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.6692</v>
+        <v>-0.673</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.2988</v>
+        <v>-0.3004</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6917</v>
+        <v>-0.712</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.6692</v>
+        <v>-0.673</v>
       </c>
       <c r="F60" t="n">
-        <v>0.5052</v>
+        <v>0.5014</v>
       </c>
       <c r="G60" t="n">
         <v>-1.1744</v>
       </c>
       <c r="H60" t="n">
-        <v>0.5052</v>
+        <v>0.5014</v>
       </c>
       <c r="I60" t="n">
         <v>0.5099</v>
@@ -3216,7 +3216,7 @@
         <v>-0.3022</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6948</v>
+        <v>-0.7136</v>
       </c>
       <c r="E61" t="n">
         <v>-0.6768999999999999</v>
@@ -3262,7 +3262,7 @@
         <v>-0.3084</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7005</v>
+        <v>-0.7192</v>
       </c>
       <c r="E62" t="n">
         <v>-0.6909</v>
@@ -3298,78 +3298,78 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Tommy</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.8914</v>
+        <v>-0.7105</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.3979</v>
+        <v>-0.3172</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7815</v>
+        <v>-0.727</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.8914</v>
+        <v>-0.7105</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.8914</v>
+        <v>-0.7105</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.8914</v>
+        <v>-0.7105</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.8914</v>
+        <v>-0.7105</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>68</v>
+        <v>209</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.8914</v>
+        <v>-0.7105</v>
       </c>
       <c r="N63" t="n">
-        <v>68</v>
+        <v>209</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ImpressioN</t>
+          <t>Tommy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.9197</v>
+        <v>-0.8914</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.4106</v>
+        <v>-0.3979</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7929</v>
+        <v>-0.799</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.9197</v>
+        <v>-0.8914</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.9197</v>
+        <v>-0.8914</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.9197</v>
+        <v>-0.8914</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.9197</v>
+        <v>-0.8914</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.9197</v>
+        <v>-0.8914</v>
       </c>
       <c r="N64" t="n">
         <v>68</v>
@@ -3390,185 +3390,185 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Lacore</t>
+          <t>ImpressioN</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.9494</v>
+        <v>-0.9197</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.4238</v>
+        <v>-0.4106</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.8103</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.9494</v>
+        <v>-0.9197</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.9494</v>
+        <v>-0.9197</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.9494</v>
+        <v>-0.9197</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.9494</v>
+        <v>-0.9197</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.9494</v>
+        <v>-0.9197</v>
       </c>
       <c r="N65" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HSK</t>
+          <t>Lacore</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-1.0128</v>
+        <v>-0.9494</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.4521</v>
+        <v>-0.4238</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8305</v>
+        <v>-0.8222</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.0128</v>
+        <v>-0.9494</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.0128</v>
+        <v>-0.9494</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-1.0128</v>
+        <v>-0.9494</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.0128</v>
+        <v>-0.9494</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-1.0128</v>
+        <v>-0.9494</v>
       </c>
       <c r="N66" t="n">
-        <v>123</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>w1nt3r</t>
+          <t>HSK</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-1.0335</v>
+        <v>-1.0128</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.4614</v>
+        <v>-0.4521</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8389</v>
+        <v>-0.8474</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.0335</v>
+        <v>-1.0128</v>
       </c>
       <c r="F67" t="n">
-        <v>-1.0335</v>
+        <v>-1.0128</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-1.0335</v>
+        <v>-1.0128</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.0335</v>
+        <v>-1.0128</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>68</v>
+        <v>123</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-1.0335</v>
+        <v>-1.0128</v>
       </c>
       <c r="N67" t="n">
-        <v>68</v>
+        <v>123</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>w1nt3r</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.0535</v>
+        <v>-1.0335</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.4703</v>
+        <v>-0.4614</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.847</v>
+        <v>-0.8557</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.0535</v>
+        <v>-1.0335</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.0535</v>
+        <v>-1.0335</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-1.0535</v>
+        <v>-1.0335</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.0535</v>
+        <v>-1.0335</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>209</v>
+        <v>68</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-1.0535</v>
+        <v>-1.0335</v>
       </c>
       <c r="N68" t="n">
-        <v>209</v>
+        <v>68</v>
       </c>
     </row>
     <row r="69">
@@ -3584,7 +3584,7 @@
         <v>-0.547</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9163</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="E69" t="n">
         <v>-1.2252</v>
@@ -3630,7 +3630,7 @@
         <v>-0.5655</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9331</v>
+        <v>-0.9486</v>
       </c>
       <c r="E70" t="n">
         <v>-1.2667</v>
@@ -3676,7 +3676,7 @@
         <v>-0.5889</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9543</v>
+        <v>-0.9695</v>
       </c>
       <c r="E71" t="n">
         <v>-1.3192</v>
@@ -3722,7 +3722,7 @@
         <v>-0.6489</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0085</v>
+        <v>-1.023</v>
       </c>
       <c r="E72" t="n">
         <v>-1.4535</v>
@@ -3762,25 +3762,25 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.4869</v>
+        <v>-1.4813</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.6637999999999999</v>
+        <v>-0.6613</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.022</v>
+        <v>-1.0341</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.4869</v>
+        <v>-1.4813</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.4869</v>
+        <v>-1.4813</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.4869</v>
+        <v>-1.4813</v>
       </c>
       <c r="I73" t="n">
         <v>-1.4938</v>
@@ -3814,7 +3814,7 @@
         <v>-0.6733</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0306</v>
+        <v>-1.0447</v>
       </c>
       <c r="E74" t="n">
         <v>-1.5081</v>
@@ -3860,7 +3860,7 @@
         <v>-0.6902</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0459</v>
+        <v>-1.0598</v>
       </c>
       <c r="E75" t="n">
         <v>-1.546</v>
@@ -3906,7 +3906,7 @@
         <v>-0.7038</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0582</v>
+        <v>-1.0719</v>
       </c>
       <c r="E76" t="n">
         <v>-1.5764</v>
@@ -3952,7 +3952,7 @@
         <v>-0.7111</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.0649</v>
+        <v>-1.0785</v>
       </c>
       <c r="E77" t="n">
         <v>-1.5929</v>
@@ -3998,7 +3998,7 @@
         <v>-0.7509</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1008</v>
+        <v>-1.114</v>
       </c>
       <c r="E78" t="n">
         <v>-1.6819</v>
@@ -4044,7 +4044,7 @@
         <v>-0.7678</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.1161</v>
+        <v>-1.1291</v>
       </c>
       <c r="E79" t="n">
         <v>-1.7198</v>
@@ -4090,7 +4090,7 @@
         <v>-1.0583</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.379</v>
+        <v>-1.3884</v>
       </c>
       <c r="E80" t="n">
         <v>-2.3706</v>
@@ -4136,7 +4136,7 @@
         <v>-1.4255</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.7113</v>
+        <v>-1.7161</v>
       </c>
       <c r="E81" t="n">
         <v>-3.1932</v>
